--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45798</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45820</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>44722</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>44459</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>44977</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44725</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44462</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>46084</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44939</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44988</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45350</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>46265</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45471</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46065</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>44657</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         <v>44571</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>44580</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>45019</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>44804</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>45079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>44984</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>45917</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>46170</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>46056</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45672</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>46084</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>46112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44942</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>45223</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4878,7 +4878,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>45573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45860</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>45253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>45440</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>44971</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>46084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>44473</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>44621</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44476</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>44592</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>44839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>44883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44467</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>44467</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>44517</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         <v>44466</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>44466</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>44475</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44564</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44514</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44532</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44536</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>44837</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>44879</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>44711</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>44652</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>44795</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>44599</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>44475</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44489</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44489</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>44636</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>44811</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>44811</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         <v>44580</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>44748</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>44658</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>44812</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>44853</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>44849</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>45196</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>45362</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>44988</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>44958</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>45001</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>44861</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>44949</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44763</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45159</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45770</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44958</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>44613</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>44792</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>44890</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>45098</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45288</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45075</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45426</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>44776</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45350</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>45222</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         <v>44879</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45240</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>44910</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>44683</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>44683</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45155</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>44879</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45327</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45309</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45001</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45001</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44998</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44987</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11850,7 +11850,7 @@
         <v>44593</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11923,7 +11923,7 @@
         <v>45051</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>45198</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>45624</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         <v>45567</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>45219</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>45163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45163</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45050</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45208</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>44967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45195</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45695</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45407</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45330</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45532</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44861</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44516</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45063</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45251</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44827</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44949</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44889</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44980</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45250</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45000</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44741</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44536</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45271</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>44944</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45225</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45583</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>44739</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45838</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>44965</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>44942</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45222</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45222</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>46092</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>44914</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>45330</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45075</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>46092</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>44795</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45271</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44795</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>44902</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45145</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45250</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45895</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>44671</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45145</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45260</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>46066</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>45798</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>45736</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>45826</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>45335</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45916</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>45917</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45917</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45917</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45917</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>45196</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>45924</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>45925</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45925</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45224</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45016</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45252</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>44490</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45408</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>46146</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45330</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45447</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>44600</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45672</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>44613</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>44706</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>44942</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>44998</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45222</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45947</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>45946</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>44965</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45132</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45951</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45329</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45139</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45369</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45001</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45001</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45624</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45966</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45054</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44841</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45194</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>44495</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45716</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45208</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45208</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45040</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45982</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45288</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>45982</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45182</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45720</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45988</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45404</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45222</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>44694</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45308</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45145</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>44988</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>44827</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45250</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45250</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>46001</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45196</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>46001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>46111</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>46111</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>44943</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>44883</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>44949</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44992</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45155</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45201</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45798</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45790</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45440</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>46169</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>44476</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>44958</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>46035</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45288</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>44984</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>44893</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>44826</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44725</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>44600</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>46174</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45029</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>45096</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>45988</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44529</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>46174</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>46174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45194</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>45113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45113</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45546</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45093</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45093</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>44881</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45328</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>46059</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45610</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45001</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44938</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>46070</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46167</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44468</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>44958</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45250</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>45250</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45243</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46084</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>46083</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>46167</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>46084</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>44739</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45113</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45113</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>46090</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46090</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>44722</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>46092</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>46092</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>44977</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>44790</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45614</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>46119</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>44985</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45093</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45093</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>46106</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44949</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>46106</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45552</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>44950</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45518</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45008</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>45178</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>46113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>44637</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44900</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>46113</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>45695</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>44851</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>44519</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>46203</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44511</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>45601</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>44640</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>45082</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         <v>45425</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27628,7 +27628,7 @@
         <v>45426</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>45012</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45583</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>46092</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45716</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45219</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>45225</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>45223</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46246</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         <v>45280</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28358,7 +28358,7 @@
         <v>45513</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28431,7 +28431,7 @@
         <v>45513</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28504,7 +28504,7 @@
         <v>45243</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45370</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45636</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>45734</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>45210</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28869,7 +28869,7 @@
         <v>45253</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45182</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29015,7 +29015,7 @@
         <v>45324</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29093,7 +29093,7 @@
         <v>45252</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>45474</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>46255</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>44657</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45194</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>46255</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>46253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>45182</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45362</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>45645</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>44502</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45027</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>45323</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>45093</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>46260</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>46217</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30261,7 +30261,7 @@
         <v>46218</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>46218</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45352</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30480,7 +30480,7 @@
         <v>46265</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45198</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45167</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45167</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>46265</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>46265</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>45977</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>46268</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>46268</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31137,7 +31137,7 @@
         <v>44986</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>45713</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>45299</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31356,7 +31356,7 @@
         <v>45474</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45694</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45665</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>46272</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31648,7 +31648,7 @@
         <v>45785</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45645</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45012</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>46278</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45330</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45474</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44679</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45527</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45665</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>46280</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45798</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45551</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>45488</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45618</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45820</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45827</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45839</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45860</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45869</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45869</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45869</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33181,7 +33181,7 @@
         <v>45880</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45713</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33327,7 +33327,7 @@
         <v>45880</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>45235</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45316</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33546,7 +33546,7 @@
         <v>45527</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45440</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44658</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
         <v>45471</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33838,7 +33838,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45440</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>45558</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34057,7 +34057,7 @@
         <v>45373</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34130,7 +34130,7 @@
         <v>44462</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45330</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34276,7 +34276,7 @@
         <v>45373</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45387</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>45373</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34495,7 +34495,7 @@
         <v>45440</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34568,7 +34568,7 @@
         <v>45687</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45440</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>44928</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>44971</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45440</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34933,7 +34933,7 @@
         <v>45791</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>45791</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35079,7 +35079,7 @@
         <v>45791</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45820</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>44722</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45426</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44977</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44725</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45330</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>46084</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>44939</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45350</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45471</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44928</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44928</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46065</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44657</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>44571</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45573</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46056</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46084</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45672</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44580</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45019</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44984</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>46265</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44804</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>46289</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44942</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45223</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45253</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45387</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45440</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45687</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44971</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46084</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44473</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>44621</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44476</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>44846</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44592</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44839</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44862</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44592</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44883</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44595</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>44467</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44467</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44489</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44466</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44466</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44475</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44564</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44514</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44532</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44536</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44837</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44879</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44652</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44795</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44599</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44489</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44475</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44489</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44811</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44811</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44580</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44748</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>44658</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>44812</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45222</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45335</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44739</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44795</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45532</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45323</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44725</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45369</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45330</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44468</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45093</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45093</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45250</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45327</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45250</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45250</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44826</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45308</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45250</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45790</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44853</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>44849</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>44942</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44949</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45798</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>44516</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>44943</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44902</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>44529</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>46035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>46035</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45618</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44511</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>44988</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45895</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45352</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44881</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44600</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45798</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45551</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45488</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45098</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>44640</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>46059</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45916</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45917</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45917</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45001</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45546</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>45008</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>45636</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45113</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45924</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45925</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>45925</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>46083</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>46084</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>46084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45155</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45583</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45720</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>46090</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>46092</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>46092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44613</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45426</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>45082</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45947</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>46106</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>46106</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>45951</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45075</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45271</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45271</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>46113</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>46113</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>44998</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45113</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45113</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45614</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44958</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44495</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45324</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45000</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45672</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45145</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44992</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45093</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>46092</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>46092</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45838</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>44739</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45988</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45425</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44776</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44985</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44694</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44683</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44683</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45243</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46001</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>46001</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>44988</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45029</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44841</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45826</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>46066</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45155</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44827</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45820</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45930</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45113</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45113</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45474</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44763</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45198</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45827</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>46146</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>44914</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44890</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>44893</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45908</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45222</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44827</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44944</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45839</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44950</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45350</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44949</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46111</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45329</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>44965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45250</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>46111</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45798</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44980</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45145</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44790</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>45860</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45288</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44984</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45051</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45988</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45567</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>44910</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>46174</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>46174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>46174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44938</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44987</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>44502</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45869</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45288</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45288</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45869</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45869</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>46167</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45016</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45513</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45513</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>46167</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45440</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45734</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44967</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45330</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>46119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45167</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45167</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>44536</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45880</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45880</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>46203</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45713</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45601</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45201</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>45063</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45624</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45027</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45253</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44795</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>44998</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45194</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>45050</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45225</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45196</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44879</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45208</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44861</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44861</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45196</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46255</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>44722</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45195</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>46253</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>46255</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>46260</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45252</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>46217</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>46218</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46218</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45250</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45161</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45159</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45182</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>45240</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45194</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45695</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45208</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46265</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46265</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45716</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45252</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>46265</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45260</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44741</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>46268</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46268</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45225</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45977</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45219</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45219</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45219</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44706</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44476</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>46272</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45330</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45552</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45198</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45280</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>46278</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46280</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44851</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44958</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45194</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45145</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44965</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45132</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46286</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45362</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45362</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>44879</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>44613</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>44600</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45093</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45093</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45075</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44977</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44637</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45196</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>46246</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44657</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45251</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>45982</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46084</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45610</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>44792</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45222</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44958</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45040</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45210</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45426</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45163</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45163</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44593</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>44958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>44519</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45001</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45001</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44490</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45370</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45224</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44949</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45624</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45139</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45058</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45309</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>44883</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45716</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45695</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>45182</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45223</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45328</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45182</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>44671</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>45036</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45012</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>44949</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45447</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45518</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45736</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45222</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45407</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45208</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45243</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45001</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45001</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>44942</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45096</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45054</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45645</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45770</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>45404</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>45408</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>45583</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45694</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45474</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45713</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45299</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44986</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45665</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45474</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>45012</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45785</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45645</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>44679</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45330</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45527</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>45665</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44658</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45235</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45316</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45527</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>45440</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45471</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45440</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45440</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>45558</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45373</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>45330</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45373</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45387</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45373</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>45440</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45687</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45440</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>44928</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44971</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45440</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45791</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45791</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45791</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45820</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>44722</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>45426</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44977</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44725</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>45202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>45330</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>46084</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>44939</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>45350</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>44988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>45471</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44928</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44928</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>46065</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>44657</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>44571</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45573</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46056</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>45917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>46084</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>46112</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>45672</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>45860</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44580</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45019</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>44984</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>45253</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>46265</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         <v>44804</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>46289</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>44942</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45223</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>45253</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45387</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>45440</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45687</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44971</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5618,7 +5618,7 @@
         <v>46084</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44473</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>44621</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44476</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>44763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>44846</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44592</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44839</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44862</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>44592</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44883</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         <v>44595</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>44467</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44467</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7037,7 +7037,7 @@
         <v>44489</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>44466</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44466</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44475</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>44564</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44514</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>44532</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44536</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>44837</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         <v>44879</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44652</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>44795</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>44599</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44489</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44475</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8278,7 +8278,7 @@
         <v>44489</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>44636</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44811</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44811</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>44516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44580</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         <v>44748</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>44658</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>44812</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>45222</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>45335</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>44739</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44795</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45532</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>45323</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44725</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         <v>45222</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45369</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>45330</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44468</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         <v>45093</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>45093</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>45250</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>45327</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45250</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45250</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44826</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45308</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45250</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>44889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45790</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44853</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>44849</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>44942</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>44949</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45798</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>44516</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>44943</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44902</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>44529</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>46035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>46035</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>45618</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44511</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>44988</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45895</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>45352</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44881</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>44600</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45798</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>45551</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>45488</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45098</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12147,7 +12147,7 @@
         <v>44640</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>46059</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         <v>45916</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12366,7 +12366,7 @@
         <v>45917</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45917</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45001</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45546</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>45008</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>45636</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13023,7 +13023,7 @@
         <v>45113</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>45924</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45925</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>45925</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         <v>46083</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13388,7 +13388,7 @@
         <v>46084</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>46084</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45155</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         <v>45583</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13680,7 +13680,7 @@
         <v>45720</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>46090</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>46092</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>46092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44613</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>45426</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>45082</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45947</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>46106</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>46106</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>45951</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45075</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45271</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45271</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>46113</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>46113</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>44998</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>45113</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45113</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45614</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44958</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15359,7 +15359,7 @@
         <v>44495</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45324</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45000</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45672</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45145</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>44992</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45093</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>46092</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>46092</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45838</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>44739</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45988</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45425</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44776</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44985</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44694</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>44683</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>44683</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45243</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>46001</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>46001</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>44988</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45029</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44841</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45826</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>46066</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45155</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44827</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45820</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45930</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45113</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45113</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45474</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44763</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45198</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45827</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>46146</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>44914</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>44890</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>44893</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45908</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45222</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>44827</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>44944</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45839</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44950</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45350</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44949</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46111</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45329</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>44965</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45250</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>46111</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45798</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>44980</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45145</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44790</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>45860</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45288</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44984</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45051</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19890,7 +19890,7 @@
         <v>45988</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>45567</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>44910</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>46174</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>46174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>46174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>44938</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44987</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>44502</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45869</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45288</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45288</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45869</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45869</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>46167</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45016</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45513</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45513</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>46167</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45440</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45734</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44967</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45330</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>46119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45167</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45167</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>44536</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45880</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45880</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>46203</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45713</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45601</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45201</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>45063</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45624</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45027</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45253</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44795</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>44998</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45194</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>45050</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45225</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45196</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44879</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45208</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44861</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>44861</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45196</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46255</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>44722</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45195</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>46253</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>46255</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>46260</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45252</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>46217</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>46218</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46218</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45250</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45161</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45159</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>45182</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>45240</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45194</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>45695</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45208</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46265</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46265</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45716</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45252</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>46265</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45260</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>44741</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>46268</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46268</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45225</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45977</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45219</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>45219</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45219</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44706</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44476</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>46272</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45330</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45552</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45198</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45280</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>46278</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>46280</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44851</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>44958</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45194</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44900</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>45145</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44965</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45132</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46286</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45362</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45362</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>44879</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>44613</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>44600</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>45093</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>45093</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45075</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>44977</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>44637</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45196</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>46246</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44657</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45251</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>45982</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46084</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45610</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>44792</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>45222</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>44958</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>45040</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>45210</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>45426</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>45163</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45163</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44593</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>44958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>44519</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45001</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29171,7 +29171,7 @@
         <v>45001</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29244,7 +29244,7 @@
         <v>44490</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45370</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>45224</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44949</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45624</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45139</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45058</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45309</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>44883</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>45716</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>45695</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>45182</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45223</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45328</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45182</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>44671</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>45036</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45012</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>44949</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30631,7 +30631,7 @@
         <v>45447</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45518</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45736</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45222</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45407</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -30996,7 +30996,7 @@
         <v>45208</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31069,7 +31069,7 @@
         <v>45243</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45001</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45001</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>44942</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45096</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45054</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45645</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45770</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>45404</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>45408</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31799,7 +31799,7 @@
         <v>45583</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31872,7 +31872,7 @@
         <v>45694</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45474</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45713</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45299</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         <v>44986</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32237,7 +32237,7 @@
         <v>45665</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45474</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>45012</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45785</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45645</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>44679</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32675,7 +32675,7 @@
         <v>45330</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45527</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32821,7 +32821,7 @@
         <v>45665</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>44658</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -32967,7 +32967,7 @@
         <v>45235</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>45316</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45527</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>45440</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33259,7 +33259,7 @@
         <v>45471</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45440</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45440</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         <v>45558</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45373</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33624,7 +33624,7 @@
         <v>45330</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33697,7 +33697,7 @@
         <v>45373</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45387</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45373</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>45440</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -33989,7 +33989,7 @@
         <v>45687</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34062,7 +34062,7 @@
         <v>45440</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>44928</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44971</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>45440</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         <v>45791</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45791</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45791</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45820</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>44722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44977</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44725</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>45330</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45350</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>45471</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>44928</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>46065</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>44657</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44571</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>44580</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45019</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45253</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44804</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45917</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>45573</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>46056</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>45079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>46084</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>44984</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>46112</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45860</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>46265</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45672</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>46289</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46293</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>44942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45223</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>45440</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>44971</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>46084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>44473</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44621</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>44476</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44592</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44489</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44475</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44564</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44514</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44532</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>44536</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44837</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44879</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44711</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44652</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44599</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44475</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44489</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44489</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44811</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44811</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44516</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44580</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44658</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44748</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44853</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45362</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45288</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44849</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45426</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44958</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45196</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44861</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45001</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44949</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45159</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45770</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44890</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44613</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44792</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45036</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44910</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45330</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45474</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44679</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>45665</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45075</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45350</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45222</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44776</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45001</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45001</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45240</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>44683</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44683</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45327</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45155</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45790</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44879</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45309</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45895</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44998</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44593</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44987</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45051</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>46035</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>46035</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45567</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45219</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45219</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45198</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45798</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45624</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45163</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45916</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45917</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>45798</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>45551</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45917</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45917</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45917</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45488</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45618</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45050</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45208</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45924</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45925</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45925</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>44967</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>46059</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45195</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45695</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45532</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45407</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45330</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44861</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45947</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45946</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45063</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44516</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44949</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>46084</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45251</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>46083</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46084</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44827</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44980</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46090</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45250</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>46092</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45000</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>46092</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45966</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44536</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>45271</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44741</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>44944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>46106</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45225</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>46106</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45583</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45820</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>44739</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>46113</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>46113</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45988</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>44965</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>44942</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45222</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45222</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45827</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44914</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>46001</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>46001</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45330</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45075</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45425</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44795</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45271</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44795</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45145</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45250</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44671</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45145</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45839</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45260</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45838</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>46092</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45736</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45335</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46092</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45196</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45224</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45016</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45252</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>46066</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>44490</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45860</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45408</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45330</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45447</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44600</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45672</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45826</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>44613</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>44706</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44942</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45869</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45869</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45869</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44998</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45930</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45222</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44965</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45132</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>45329</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>46146</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45139</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45369</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45001</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45624</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45908</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44841</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45194</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>44495</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45716</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45208</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45208</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45040</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>46111</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45288</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>46111</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45880</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45713</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45798</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45880</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45182</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45288</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44984</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45720</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46174</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45988</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45404</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46174</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45222</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44694</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45308</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45145</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44988</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>46167</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>44827</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45250</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45250</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46167</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45196</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>46119</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44943</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>44883</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44949</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44992</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45155</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45201</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45440</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44476</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46203</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44958</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45253</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44893</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>44826</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>44725</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44600</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45029</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45096</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>44529</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>46260</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45113</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>46217</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45546</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>46218</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>46218</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45093</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45093</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>46265</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44881</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>46265</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45328</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45610</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>46265</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45001</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44938</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45161</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45084</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45977</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>46268</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>46268</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45113</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44958</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45250</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45250</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>46272</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45243</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>46278</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44739</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45113</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>45113</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>44722</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>46280</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>44977</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44790</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45614</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44985</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45093</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45093</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>44949</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45552</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>46286</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>44950</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45518</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45008</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45178</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44637</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44900</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45695</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>46246</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44851</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45982</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44519</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>46293</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44511</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45601</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44640</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45082</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>46084</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45426</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45012</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45583</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>45716</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45219</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45225</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45223</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45280</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45513</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45513</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>46255</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45243</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45370</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>45636</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>46255</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45734</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>46253</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45210</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>45182</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45324</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45252</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45474</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44657</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45194</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45182</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45362</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45645</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>44502</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>45027</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45323</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>45093</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45352</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45198</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45167</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45167</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>44986</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45713</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>45299</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45474</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45694</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45665</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45785</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>45645</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45012</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45235</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45527</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45440</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>44658</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45471</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45440</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45440</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45558</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45373</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45330</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45373</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45373</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>45687</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45440</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>44928</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>44971</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45440</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45791</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45791</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45791</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45820</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>44722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         <v>45202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>44977</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44725</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>45426</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>45330</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>44939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>46265</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45350</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>45471</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>44928</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>46065</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>44657</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44571</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>44580</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45019</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45253</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44804</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45917</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>45573</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>46056</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>45079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>46084</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>44984</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>46112</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45860</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>46265</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45672</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44596</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>46289</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46293</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>44942</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>45223</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>45440</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>44971</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>46084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>44473</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44621</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>44476</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44592</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44489</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44475</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44564</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44514</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44532</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>44536</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44837</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44879</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44711</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44652</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44599</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44475</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44489</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44489</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44811</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44811</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44516</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44580</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44658</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44812</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44748</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44853</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45362</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45288</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>44849</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45426</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44958</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45196</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>44861</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45001</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44949</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44763</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45159</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45770</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44890</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44958</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44613</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44792</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45036</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44910</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45098</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45330</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45474</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44679</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>45665</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45075</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45350</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>45222</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44776</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45001</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45001</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45240</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>44683</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44683</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45327</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45155</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45790</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44879</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45309</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45895</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44998</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44593</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44987</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45051</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>46035</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>46035</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45567</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45219</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45219</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>45198</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>45798</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45624</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>45163</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>45916</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45917</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>45798</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>45551</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45917</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45917</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45917</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45488</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45618</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>45050</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45208</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45924</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45925</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45925</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>44967</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>46059</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45195</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45695</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45532</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45407</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45330</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>44861</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45947</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45946</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45063</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44516</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44949</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>46084</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45251</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>46083</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>46084</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44827</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>44980</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>44889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>46090</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45250</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>46092</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45000</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>46092</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45966</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44536</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>45271</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44741</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>44944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>46106</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45225</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>46106</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45583</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45820</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>44739</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>46113</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>46113</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45988</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>44965</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>44942</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45222</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45222</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45827</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44914</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>46001</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>46001</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45330</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45075</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45425</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44795</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45271</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44795</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45145</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45250</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44671</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45145</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45839</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45260</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45838</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>46092</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45736</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45335</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46092</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45196</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45224</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45016</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45252</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>46066</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>44490</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45860</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45408</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45330</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45447</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44600</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45672</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45826</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>44613</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>44706</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44942</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45869</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45869</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45869</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44998</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45930</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45222</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>44965</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45132</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>45329</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>46146</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45139</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45369</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45001</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45001</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45624</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45908</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44841</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>45194</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>44495</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45716</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45208</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45208</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45040</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>46111</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45288</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>46111</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45880</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45713</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45798</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22147,7 +22147,7 @@
         <v>45880</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45182</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45288</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>44984</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>45720</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>46174</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45058</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45988</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45404</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22804,7 +22804,7 @@
         <v>46174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46174</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45222</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44694</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45308</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45145</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44988</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>46167</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>44827</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45250</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45250</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46167</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23680,7 +23680,7 @@
         <v>45196</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23753,7 +23753,7 @@
         <v>46119</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         <v>44943</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>44883</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>44949</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44992</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45155</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>45201</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45440</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>44476</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>46203</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24483,7 +24483,7 @@
         <v>44958</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45253</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>44893</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>44826</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>44725</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44600</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45029</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45096</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>44529</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>46260</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45113</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>46217</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45546</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>46218</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>46218</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45093</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45093</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>46265</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44881</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>46265</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45328</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45610</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>46265</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45001</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44938</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45161</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45084</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45977</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>46268</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>46268</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45113</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44958</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26970,7 +26970,7 @@
         <v>45250</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45250</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27116,7 +27116,7 @@
         <v>46272</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>45243</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27262,7 +27262,7 @@
         <v>46278</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44739</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45113</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27481,7 +27481,7 @@
         <v>45113</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>44722</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         <v>46280</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>44977</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44790</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45614</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44985</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>45093</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28065,7 +28065,7 @@
         <v>45093</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>44949</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45552</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28284,7 +28284,7 @@
         <v>46286</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>44950</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28430,7 +28430,7 @@
         <v>45518</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28503,7 +28503,7 @@
         <v>45008</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45178</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>44637</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44900</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45695</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>46246</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44851</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29014,7 +29014,7 @@
         <v>45982</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29087,7 +29087,7 @@
         <v>44519</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         <v>46293</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>44511</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>45601</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>44640</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45082</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>46084</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45426</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45012</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45583</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>45716</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45219</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45225</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>45223</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>45280</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45513</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45513</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>46255</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>45243</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>45370</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30547,7 +30547,7 @@
         <v>45636</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>46255</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45734</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         <v>46253</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>45210</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>45182</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45324</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45252</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>45474</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>44657</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45194</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45182</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45362</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45645</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>44502</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>45027</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45323</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>45093</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45352</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>45198</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45167</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>45167</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>44986</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45713</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>45299</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>45474</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45694</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45665</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45785</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>45645</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45012</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45235</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45527</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45440</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>44658</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45471</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45440</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45440</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45558</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45373</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45330</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45373</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>45373</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>45687</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45440</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>44928</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>44971</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45440</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34275,7 +34275,7 @@
         <v>45791</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45791</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45791</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45820</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>44722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>45426</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45350</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44725</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>45330</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>45350</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>46265</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>45471</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>44928</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>46065</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>44657</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44571</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>45223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>44580</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45019</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>44984</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45917</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>45573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>45253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45672</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>45860</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44804</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>45079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44942</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>46056</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>46084</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>46289</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>46293</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>45253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>45440</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>44971</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>46084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>44621</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>44763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>44846</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44592</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>44530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44839</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44862</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>44592</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44883</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44595</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44517</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44652</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44795</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44599</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44564</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44489</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>44514</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44536</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44879</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44636</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44532</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44811</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44748</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44658</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44890</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>45369</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44893</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>45139</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45093</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45093</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45335</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45058</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45309</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45222</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45222</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44827</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44883</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44944</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>44739</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44795</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45716</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45695</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>45323</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45182</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44950</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45532</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45250</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>45327</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45350</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>45250</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v>45250</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44949</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>45223</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>45329</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>44965</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45250</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44725</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44826</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>45328</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>45308</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45250</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>44980</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>45182</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         <v>45145</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>44671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44889</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45036</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45012</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>44949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>44853</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45447</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44849</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45518</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>44790</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45736</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>45222</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45051</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44942</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         <v>45567</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         <v>45407</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>44910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>44516</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         <v>45208</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>44943</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         <v>44902</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45243</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>45001</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>45895</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>44942</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>44529</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         <v>45096</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>45054</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         <v>45645</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>45770</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>44938</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44987</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>44502</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>44988</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45404</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45798</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45408</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45352</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>45288</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45288</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45583</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45694</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45474</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45713</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45299</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44881</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44986</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44600</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45016</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
         <v>45665</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>45916</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45474</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15645,7 +15645,7 @@
         <v>45012</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45785</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45098</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>45917</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44679</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>45917</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45330</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45513</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45513</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45527</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45001</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45001</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45546</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45008</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45440</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45734</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45924</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44967</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45925</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45665</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45636</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45113</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45925</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45330</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45167</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44536</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45155</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45798</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45583</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45601</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45618</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45201</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45551</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45488</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45063</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>44613</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45624</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45027</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>44795</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45426</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45082</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44998</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45194</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45050</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45225</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>44879</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45208</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45075</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45271</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45271</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>44861</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>44861</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19952,7 +19952,7 @@
         <v>45196</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45947</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>44722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44998</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20244,7 +20244,7 @@
         <v>45195</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45113</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45113</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>45946</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         <v>45820</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>44958</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45827</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44495</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45252</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45951</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45324</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>45000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45672</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
         <v>45250</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
         <v>45161</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>45145</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>45159</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45182</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>45240</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         <v>44992</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45966</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45839</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45093</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>45194</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45695</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>45208</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45178</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>44739</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45716</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44776</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>45260</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>44741</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22736,7 +22736,7 @@
         <v>44985</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45860</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22882,7 +22882,7 @@
         <v>44694</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44683</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>44683</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45225</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>45243</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45219</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45219</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45219</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>44706</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45869</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45869</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>45869</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>44988</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45029</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45330</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>44841</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45155</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45552</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>44827</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>45880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>45880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45713</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45198</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45113</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24634,7 +24634,7 @@
         <v>45113</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>45474</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45280</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>44763</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>44851</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>44958</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25223,7 +25223,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25296,7 +25296,7 @@
         <v>46106</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>45988</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25442,7 +25442,7 @@
         <v>44900</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>45145</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45132</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>44914</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         <v>45362</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45362</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
         <v>44879</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>44613</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>46001</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>44600</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45093</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45093</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>46001</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45075</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>44977</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26610,7 +26610,7 @@
         <v>46092</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>46092</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>45838</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>44637</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45196</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>44657</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45251</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45425</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>45790</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45610</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>44792</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45222</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44958</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>45040</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>45210</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45826</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>46066</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>45426</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>46035</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>45163</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28070,7 +28070,7 @@
         <v>45163</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>44593</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>44958</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>44519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         <v>45001</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28508,7 +28508,7 @@
         <v>45001</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44490</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45930</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45370</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45224</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>44949</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45624</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>46059</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>46146</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>46083</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>46084</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>46084</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45908</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>46090</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>46092</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>46092</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>46111</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>46111</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45798</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45288</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>44984</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45988</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>46174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>46174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>46174</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>46167</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>46167</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>46119</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>46203</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45253</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>46217</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>46218</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>46218</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30917,7 +30917,7 @@
         <v>46265</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>46265</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>46265</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31136,7 +31136,7 @@
         <v>46268</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31209,7 +31209,7 @@
         <v>46268</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45977</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>46272</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>46278</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>46280</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>46286</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>46246</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45982</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>46084</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>46293</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31939,7 +31939,7 @@
         <v>46255</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>46255</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         <v>46300</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32158,7 +32158,7 @@
         <v>46253</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>46113</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32304,7 +32304,7 @@
         <v>46302</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32377,7 +32377,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>46304</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>44658</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45235</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>45316</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32742,7 +32742,7 @@
         <v>45527</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         <v>45440</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45471</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>45440</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45440</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45558</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45373</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>45330</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45373</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45387</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45373</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45440</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45687</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45440</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>44928</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>44971</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>45440</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>45791</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34056,7 +34056,7 @@
         <v>45791</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>45791</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 28946-2025</t>
+          <t>A 18694-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,14 +939,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45820</v>
+        <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -983,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -998,6 +998,118 @@
         <v>4</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Grovticka
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0834/artfynd/A 18694-2024 artfynd.xlsx", "A 18694-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor/A 18694-2024 karta.png", "A 18694-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor_geotiff/A 18694-2024 georefererad karta.tif", "A 18694-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomål/A 18694-2024 FSC-klagomål.docx", "A 18694-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomålsmail/A 18694-2024 FSC-klagomål mail.docx", "A 18694-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsyn/A 18694-2024 tillsynsbegäran.docx", "A 18694-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsynsmail/A 18694-2024 tillsynsbegäran mail.docx", "A 18694-2024")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0834/fåglar/A 18694-2024 prioriterade fågelarter.docx", "A 18694-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 28946-2025</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45820</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TORSÅS</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Korskovall
 Krusfrö
@@ -1005,107 +1117,107 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/artfynd/A 28946-2025 artfynd.xlsx", "A 28946-2025")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor/A 28946-2025 karta.png", "A 28946-2025")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor_geotiff/A 28946-2025 georefererad karta.tif", "A 28946-2025")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomål/A 28946-2025 FSC-klagomål.docx", "A 28946-2025")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomålsmail/A 28946-2025 FSC-klagomål mail.docx", "A 28946-2025")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsyn/A 28946-2025 tillsynsbegäran.docx", "A 28946-2025")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsynsmail/A 28946-2025 tillsynsbegäran mail.docx", "A 28946-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>A 24660-2025</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>45798</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>TORSÅS</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TORSÅS</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>2.3</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Sydpipistrell
 Nordfladdermus
@@ -1113,107 +1225,107 @@
 Större brunfladdermus</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/artfynd/A 24660-2025 artfynd.xlsx", "A 24660-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor/A 24660-2025 karta.png", "A 24660-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor_geotiff/A 24660-2025 georefererad karta.tif", "A 24660-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomål/A 24660-2025 FSC-klagomål.docx", "A 24660-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomålsmail/A 24660-2025 FSC-klagomål mail.docx", "A 24660-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsyn/A 24660-2025 tillsynsbegäran.docx", "A 24660-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsynsmail/A 24660-2025 tillsynsbegäran mail.docx", "A 24660-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 40199-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>TORSÅS</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="E8" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TORSÅS</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>1.1</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>4</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Slåtterfibbla
 Tvåblad
@@ -1221,107 +1333,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/artfynd/A 40199-2026 artfynd.xlsx", "A 40199-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor/A 40199-2026 karta.png", "A 40199-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor_geotiff/A 40199-2026 georefererad karta.tif", "A 40199-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomål/A 40199-2026 FSC-klagomål.docx", "A 40199-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomålsmail/A 40199-2026 FSC-klagomål mail.docx", "A 40199-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsyn/A 40199-2026 tillsynsbegäran.docx", "A 40199-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsynsmail/A 40199-2026 tillsynsbegäran mail.docx", "A 40199-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>S 3173-2022</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>44722</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>TORSÅS</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TORSÅS</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>8.5</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N9" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>4</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R9" t="n">
         <v>3</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S9" t="n">
         <v>4</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>5</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Kattmynta
@@ -1329,143 +1441,32 @@
 Sumpviol</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/artfynd/S 3173-2022 artfynd.xlsx", "S 3173-2022")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor/S 3173-2022 karta.png", "S 3173-2022")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor_geotiff/S 3173-2022 georefererad karta.tif", "S 3173-2022")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomål/S 3173-2022 FSC-klagomål.docx", "S 3173-2022")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomålsmail/S 3173-2022 FSC-klagomål mail.docx", "S 3173-2022")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsyn/S 3173-2022 tillsynsbegäran.docx", "S 3173-2022")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsynsmail/S 3173-2022 tillsynsbegäran mail.docx", "S 3173-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 18694-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45426</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>TORSÅS</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0834/artfynd/A 18694-2024 artfynd.xlsx", "A 18694-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor/A 18694-2024 karta.png", "A 18694-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0834/kartor_geotiff/A 18694-2024 georefererad karta.tif", "A 18694-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomål/A 18694-2024 FSC-klagomål.docx", "A 18694-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0834/klagomålsmail/A 18694-2024 FSC-klagomål mail.docx", "A 18694-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsyn/A 18694-2024 tillsynsbegäran.docx", "A 18694-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0834/tillsynsmail/A 18694-2024 tillsynsbegäran mail.docx", "A 18694-2024")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0834/fåglar/A 18694-2024 prioriterade fågelarter.docx", "A 18694-2024")</f>
         <v/>
       </c>
     </row>
@@ -1489,7 +1490,7 @@
         <v>45202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1597,7 @@
         <v>45350</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1704,7 @@
         <v>44725</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1810,7 +1811,7 @@
         <v>44977</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1918,7 @@
         <v>45330</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2024,7 +2025,7 @@
         <v>46084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2131,7 +2132,7 @@
         <v>45350</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2238,7 @@
         <v>44988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2348,7 @@
         <v>44939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2453,7 +2454,7 @@
         <v>46265</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2559,7 +2560,7 @@
         <v>45471</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2665,7 +2666,7 @@
         <v>44928</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2771,7 +2772,7 @@
         <v>44928</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2877,7 +2878,7 @@
         <v>46065</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2983,7 +2984,7 @@
         <v>44657</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3088,7 +3089,7 @@
         <v>44571</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3197,7 +3198,7 @@
         <v>45223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3302,7 +3303,7 @@
         <v>44580</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3407,7 +3408,7 @@
         <v>45019</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3512,7 +3513,7 @@
         <v>44984</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3617,7 +3618,7 @@
         <v>45917</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3722,7 +3723,7 @@
         <v>44596</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3827,7 +3828,7 @@
         <v>45573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3937,7 +3938,7 @@
         <v>45253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4043,7 @@
         <v>45672</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4147,7 +4148,7 @@
         <v>45860</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4252,7 +4253,7 @@
         <v>44804</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4357,7 +4358,7 @@
         <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4462,7 +4463,7 @@
         <v>45079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4567,7 +4568,7 @@
         <v>44942</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4672,7 +4673,7 @@
         <v>46056</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4777,7 +4778,7 @@
         <v>46084</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4882,7 +4883,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4987,7 +4988,7 @@
         <v>46289</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5092,7 +5093,7 @@
         <v>46293</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5197,7 +5198,7 @@
         <v>45253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5302,7 +5303,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5407,7 +5408,7 @@
         <v>45440</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5512,7 +5513,7 @@
         <v>45687</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5617,7 +5618,7 @@
         <v>44971</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5726,7 +5727,7 @@
         <v>45387</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5831,7 +5832,7 @@
         <v>46084</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5936,7 +5937,7 @@
         <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6009,7 +6010,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6082,7 +6083,7 @@
         <v>44621</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6155,7 +6156,7 @@
         <v>44763</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6228,7 +6229,7 @@
         <v>44846</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6301,7 +6302,7 @@
         <v>44592</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6374,7 +6375,7 @@
         <v>44530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6447,7 +6448,7 @@
         <v>44839</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6520,7 +6521,7 @@
         <v>44586</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6593,7 +6594,7 @@
         <v>44862</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6666,7 +6667,7 @@
         <v>44592</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6739,7 +6740,7 @@
         <v>44883</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6812,7 +6813,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6885,7 +6886,7 @@
         <v>44595</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6958,7 +6959,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7031,7 +7032,7 @@
         <v>44517</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7104,7 +7105,7 @@
         <v>44652</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7177,7 +7178,7 @@
         <v>44795</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7250,7 +7251,7 @@
         <v>44489</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7323,7 +7324,7 @@
         <v>44599</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7396,7 +7397,7 @@
         <v>44564</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7469,7 +7470,7 @@
         <v>44489</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7542,7 +7543,7 @@
         <v>44514</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7615,7 +7616,7 @@
         <v>44536</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7688,7 +7689,7 @@
         <v>44837</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7761,7 +7762,7 @@
         <v>44879</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7834,7 +7835,7 @@
         <v>44636</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7907,7 +7908,7 @@
         <v>44711</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7980,7 +7981,7 @@
         <v>44532</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8053,7 +8054,7 @@
         <v>44811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8126,7 +8127,7 @@
         <v>44811</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8199,7 +8200,7 @@
         <v>44516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8272,7 +8273,7 @@
         <v>44580</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8345,7 +8346,7 @@
         <v>44748</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8418,7 +8419,7 @@
         <v>44658</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8491,7 +8492,7 @@
         <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8564,7 +8565,7 @@
         <v>44890</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8637,7 +8638,7 @@
         <v>44812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8710,7 +8711,7 @@
         <v>45369</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8783,7 +8784,7 @@
         <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8856,7 +8857,7 @@
         <v>44893</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8929,7 +8930,7 @@
         <v>45139</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9002,7 +9003,7 @@
         <v>45093</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9075,7 +9076,7 @@
         <v>45093</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9148,7 +9149,7 @@
         <v>45335</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9221,7 +9222,7 @@
         <v>45058</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9294,7 +9295,7 @@
         <v>45309</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9367,7 +9368,7 @@
         <v>45222</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9440,7 +9441,7 @@
         <v>45222</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9513,7 +9514,7 @@
         <v>44827</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9586,7 +9587,7 @@
         <v>44883</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9659,7 +9660,7 @@
         <v>44944</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9732,7 +9733,7 @@
         <v>44739</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9805,7 +9806,7 @@
         <v>44795</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9878,7 +9879,7 @@
         <v>45716</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9951,7 +9952,7 @@
         <v>45695</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10024,7 +10025,7 @@
         <v>45323</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10097,7 +10098,7 @@
         <v>45182</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10170,7 +10171,7 @@
         <v>44950</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10243,7 +10244,7 @@
         <v>45532</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10316,7 +10317,7 @@
         <v>45250</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10389,7 +10390,7 @@
         <v>45327</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10462,7 +10463,7 @@
         <v>45350</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10535,7 +10536,7 @@
         <v>45250</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10608,7 +10609,7 @@
         <v>45250</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10681,7 +10682,7 @@
         <v>44949</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10754,7 +10755,7 @@
         <v>45223</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10827,7 +10828,7 @@
         <v>45329</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10900,7 +10901,7 @@
         <v>44965</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10973,7 +10974,7 @@
         <v>45250</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11046,7 +11047,7 @@
         <v>44725</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11119,7 +11120,7 @@
         <v>44826</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11192,7 +11193,7 @@
         <v>45328</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11265,7 +11266,7 @@
         <v>45308</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11338,7 +11339,7 @@
         <v>45250</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11411,7 +11412,7 @@
         <v>44980</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11484,7 +11485,7 @@
         <v>45182</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11557,7 +11558,7 @@
         <v>45145</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11630,7 +11631,7 @@
         <v>44671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11703,7 +11704,7 @@
         <v>44889</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11776,7 +11777,7 @@
         <v>45036</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11849,7 +11850,7 @@
         <v>45012</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11922,7 +11923,7 @@
         <v>44949</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11995,7 +11996,7 @@
         <v>44853</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12068,7 +12069,7 @@
         <v>45447</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12141,7 +12142,7 @@
         <v>44849</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12214,7 +12215,7 @@
         <v>45518</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12287,7 +12288,7 @@
         <v>44790</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12360,7 +12361,7 @@
         <v>45736</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12433,7 +12434,7 @@
         <v>45222</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12506,7 +12507,7 @@
         <v>45051</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12579,7 +12580,7 @@
         <v>44942</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12652,7 +12653,7 @@
         <v>44949</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12725,7 +12726,7 @@
         <v>45567</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12798,7 +12799,7 @@
         <v>45407</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12871,7 +12872,7 @@
         <v>44910</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12944,7 +12945,7 @@
         <v>44516</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13017,7 +13018,7 @@
         <v>45208</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13090,7 +13091,7 @@
         <v>44943</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13163,7 +13164,7 @@
         <v>44902</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13236,7 +13237,7 @@
         <v>45243</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13309,7 +13310,7 @@
         <v>45001</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13382,7 +13383,7 @@
         <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13455,7 +13456,7 @@
         <v>45895</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13528,7 +13529,7 @@
         <v>44942</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13601,7 +13602,7 @@
         <v>44529</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13674,7 +13675,7 @@
         <v>45096</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13747,7 +13748,7 @@
         <v>45054</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13820,7 +13821,7 @@
         <v>45645</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13893,7 +13894,7 @@
         <v>45770</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13966,7 +13967,7 @@
         <v>44938</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14039,7 +14040,7 @@
         <v>44987</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14112,7 +14113,7 @@
         <v>44502</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14185,7 +14186,7 @@
         <v>44511</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14258,7 +14259,7 @@
         <v>44988</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14331,7 +14332,7 @@
         <v>45404</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14404,7 +14405,7 @@
         <v>45798</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14477,7 +14478,7 @@
         <v>45408</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14550,7 +14551,7 @@
         <v>45352</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14623,7 +14624,7 @@
         <v>45288</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14696,7 +14697,7 @@
         <v>45288</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14769,7 +14770,7 @@
         <v>45583</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14842,7 +14843,7 @@
         <v>45694</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14915,7 +14916,7 @@
         <v>45474</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14988,7 +14989,7 @@
         <v>45713</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15061,7 +15062,7 @@
         <v>45299</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15134,7 +15135,7 @@
         <v>44881</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15207,7 +15208,7 @@
         <v>44986</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15280,7 +15281,7 @@
         <v>44600</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15353,7 +15354,7 @@
         <v>45016</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15426,7 +15427,7 @@
         <v>45665</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15499,7 +15500,7 @@
         <v>45916</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15572,7 +15573,7 @@
         <v>45474</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15645,7 +15646,7 @@
         <v>45012</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15718,7 +15719,7 @@
         <v>45785</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15791,7 +15792,7 @@
         <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15864,7 +15865,7 @@
         <v>45098</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15937,7 +15938,7 @@
         <v>45917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16010,7 +16011,7 @@
         <v>45917</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16083,7 +16084,7 @@
         <v>44679</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16156,7 +16157,7 @@
         <v>45917</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16229,7 +16230,7 @@
         <v>45917</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16302,7 +16303,7 @@
         <v>45330</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16375,7 +16376,7 @@
         <v>45513</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16448,7 +16449,7 @@
         <v>45513</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16521,7 +16522,7 @@
         <v>45527</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16594,7 +16595,7 @@
         <v>45001</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16667,7 +16668,7 @@
         <v>45001</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16740,7 +16741,7 @@
         <v>45546</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16813,7 +16814,7 @@
         <v>45008</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16886,7 +16887,7 @@
         <v>45440</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16959,7 +16960,7 @@
         <v>45734</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17032,7 +17033,7 @@
         <v>45084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17105,7 +17106,7 @@
         <v>45924</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17178,7 +17179,7 @@
         <v>44967</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17251,7 +17252,7 @@
         <v>45925</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17324,7 +17325,7 @@
         <v>45665</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17397,7 +17398,7 @@
         <v>45636</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17470,7 +17471,7 @@
         <v>45113</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17543,7 +17544,7 @@
         <v>45925</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17616,7 +17617,7 @@
         <v>45330</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17689,7 +17690,7 @@
         <v>45167</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17762,7 +17763,7 @@
         <v>45167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17835,7 +17836,7 @@
         <v>44536</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17908,7 +17909,7 @@
         <v>45155</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17981,7 +17982,7 @@
         <v>45798</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18054,7 +18055,7 @@
         <v>45583</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18127,7 +18128,7 @@
         <v>45720</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18200,7 +18201,7 @@
         <v>45601</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18273,7 +18274,7 @@
         <v>45618</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18346,7 +18347,7 @@
         <v>45201</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18419,7 +18420,7 @@
         <v>45551</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18492,7 +18493,7 @@
         <v>45488</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18565,7 +18566,7 @@
         <v>45063</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18638,7 +18639,7 @@
         <v>44613</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18711,7 +18712,7 @@
         <v>45624</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18784,7 +18785,7 @@
         <v>45027</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18857,7 +18858,7 @@
         <v>44795</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18930,7 +18931,7 @@
         <v>45426</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19003,7 +19004,7 @@
         <v>45082</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19076,7 +19077,7 @@
         <v>44998</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19149,7 +19150,7 @@
         <v>45194</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19222,7 +19223,7 @@
         <v>45050</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19295,7 +19296,7 @@
         <v>45225</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19368,7 +19369,7 @@
         <v>45196</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19441,7 +19442,7 @@
         <v>44879</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19514,7 +19515,7 @@
         <v>45208</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19587,7 +19588,7 @@
         <v>45075</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19660,7 +19661,7 @@
         <v>45271</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19733,7 +19734,7 @@
         <v>45271</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19806,7 +19807,7 @@
         <v>44861</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19879,7 +19880,7 @@
         <v>44861</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19952,7 +19953,7 @@
         <v>45196</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20025,7 +20026,7 @@
         <v>45947</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20098,7 +20099,7 @@
         <v>44722</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20171,7 +20172,7 @@
         <v>44998</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20244,7 +20245,7 @@
         <v>45195</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20317,7 +20318,7 @@
         <v>45113</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20390,7 +20391,7 @@
         <v>45113</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20463,7 +20464,7 @@
         <v>45946</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20536,7 +20537,7 @@
         <v>45820</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20609,7 +20610,7 @@
         <v>45614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20682,7 +20683,7 @@
         <v>44958</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20755,7 +20756,7 @@
         <v>45827</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20828,7 +20829,7 @@
         <v>44495</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20901,7 +20902,7 @@
         <v>45252</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20974,7 +20975,7 @@
         <v>45951</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21047,7 +21048,7 @@
         <v>45324</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21125,7 +21126,7 @@
         <v>45000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21198,7 +21199,7 @@
         <v>45672</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21271,7 +21272,7 @@
         <v>45250</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21344,7 +21345,7 @@
         <v>45161</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21417,7 +21418,7 @@
         <v>45145</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21490,7 +21491,7 @@
         <v>45159</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21563,7 +21564,7 @@
         <v>45182</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21636,7 +21637,7 @@
         <v>45240</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21709,7 +21710,7 @@
         <v>44992</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21782,7 +21783,7 @@
         <v>45966</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21855,7 +21856,7 @@
         <v>45839</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21928,7 +21929,7 @@
         <v>45093</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22001,7 +22002,7 @@
         <v>45194</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22079,7 +22080,7 @@
         <v>45695</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22152,7 +22153,7 @@
         <v>45208</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22225,7 +22226,7 @@
         <v>45178</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22298,7 +22299,7 @@
         <v>44739</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22371,7 +22372,7 @@
         <v>45716</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22444,7 +22445,7 @@
         <v>44776</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22517,7 +22518,7 @@
         <v>45252</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22590,7 +22591,7 @@
         <v>45260</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22663,7 +22664,7 @@
         <v>44741</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22736,7 +22737,7 @@
         <v>44985</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22809,7 +22810,7 @@
         <v>45860</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22882,7 +22883,7 @@
         <v>44694</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22955,7 +22956,7 @@
         <v>44683</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23028,7 +23029,7 @@
         <v>44683</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23101,7 +23102,7 @@
         <v>45225</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23174,7 +23175,7 @@
         <v>45243</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23247,7 +23248,7 @@
         <v>45219</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23320,7 +23321,7 @@
         <v>45219</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23393,7 +23394,7 @@
         <v>45219</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23466,7 +23467,7 @@
         <v>44706</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23539,7 +23540,7 @@
         <v>45869</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23612,7 +23613,7 @@
         <v>45869</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23685,7 +23686,7 @@
         <v>45869</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23758,7 +23759,7 @@
         <v>44988</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23831,7 +23832,7 @@
         <v>45029</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23904,7 +23905,7 @@
         <v>45330</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23977,7 +23978,7 @@
         <v>44841</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24050,7 +24051,7 @@
         <v>45155</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24123,7 +24124,7 @@
         <v>45552</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24196,7 +24197,7 @@
         <v>44827</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24269,7 +24270,7 @@
         <v>45880</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24342,7 +24343,7 @@
         <v>45880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24415,7 +24416,7 @@
         <v>45713</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24488,7 +24489,7 @@
         <v>45198</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24561,7 +24562,7 @@
         <v>45113</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24634,7 +24635,7 @@
         <v>45113</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24707,7 +24708,7 @@
         <v>45474</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24780,7 +24781,7 @@
         <v>45280</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24853,7 +24854,7 @@
         <v>44763</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24926,7 +24927,7 @@
         <v>44851</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24999,7 +25000,7 @@
         <v>45198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25072,7 +25073,7 @@
         <v>44958</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25150,7 +25151,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25223,7 +25224,7 @@
         <v>46106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25296,7 +25297,7 @@
         <v>46106</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25369,7 +25370,7 @@
         <v>45988</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25442,7 +25443,7 @@
         <v>44900</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25515,7 +25516,7 @@
         <v>45145</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25588,7 +25589,7 @@
         <v>44965</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25661,7 +25662,7 @@
         <v>45132</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25734,7 +25735,7 @@
         <v>44914</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25807,7 +25808,7 @@
         <v>45362</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25880,7 +25881,7 @@
         <v>45362</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25953,7 +25954,7 @@
         <v>44879</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26026,7 +26027,7 @@
         <v>44613</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26099,7 +26100,7 @@
         <v>46001</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26172,7 +26173,7 @@
         <v>44600</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26245,7 +26246,7 @@
         <v>45093</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26318,7 +26319,7 @@
         <v>45093</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26391,7 +26392,7 @@
         <v>46001</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26464,7 +26465,7 @@
         <v>45075</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26537,7 +26538,7 @@
         <v>44977</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26610,7 +26611,7 @@
         <v>46092</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26683,7 +26684,7 @@
         <v>46092</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26756,7 +26757,7 @@
         <v>45838</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26829,7 +26830,7 @@
         <v>44637</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26902,7 +26903,7 @@
         <v>45196</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26975,7 +26976,7 @@
         <v>44657</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27048,7 +27049,7 @@
         <v>45251</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27121,7 +27122,7 @@
         <v>45425</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27194,7 +27195,7 @@
         <v>45790</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27267,7 +27268,7 @@
         <v>45610</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27340,7 +27341,7 @@
         <v>44792</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27413,7 +27414,7 @@
         <v>45222</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27486,7 +27487,7 @@
         <v>44958</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27559,7 +27560,7 @@
         <v>45040</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27632,7 +27633,7 @@
         <v>45210</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27705,7 +27706,7 @@
         <v>45826</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27778,7 +27779,7 @@
         <v>46066</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27851,7 +27852,7 @@
         <v>45426</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27924,7 +27925,7 @@
         <v>46035</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27997,7 +27998,7 @@
         <v>45163</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28070,7 +28071,7 @@
         <v>45163</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28143,7 +28144,7 @@
         <v>46035</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28216,7 +28217,7 @@
         <v>44593</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28289,7 +28290,7 @@
         <v>44958</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28362,7 +28363,7 @@
         <v>44519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28435,7 +28436,7 @@
         <v>45001</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28508,7 +28509,7 @@
         <v>45001</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28581,7 +28582,7 @@
         <v>44490</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28654,7 +28655,7 @@
         <v>45930</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28727,7 +28728,7 @@
         <v>45370</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28800,7 +28801,7 @@
         <v>45224</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28873,7 +28874,7 @@
         <v>44949</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28946,7 +28947,7 @@
         <v>45624</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29019,7 +29020,7 @@
         <v>46059</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29092,7 +29093,7 @@
         <v>46146</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29165,7 +29166,7 @@
         <v>46083</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29238,7 +29239,7 @@
         <v>46084</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29311,7 +29312,7 @@
         <v>46084</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29384,7 +29385,7 @@
         <v>45908</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29457,7 +29458,7 @@
         <v>46090</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29530,7 +29531,7 @@
         <v>46092</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29603,7 +29604,7 @@
         <v>46092</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29676,7 +29677,7 @@
         <v>46111</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29749,7 +29750,7 @@
         <v>46111</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29822,7 +29823,7 @@
         <v>45798</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29895,7 +29896,7 @@
         <v>45288</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29968,7 +29969,7 @@
         <v>44984</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30041,7 +30042,7 @@
         <v>45988</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30114,7 +30115,7 @@
         <v>46174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30187,7 +30188,7 @@
         <v>46174</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30260,7 +30261,7 @@
         <v>46174</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30333,7 +30334,7 @@
         <v>46167</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30406,7 +30407,7 @@
         <v>46167</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30479,7 +30480,7 @@
         <v>46119</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30552,7 +30553,7 @@
         <v>46203</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30625,7 +30626,7 @@
         <v>45253</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30698,7 +30699,7 @@
         <v>46217</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30771,7 +30772,7 @@
         <v>46218</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30844,7 +30845,7 @@
         <v>46218</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30917,7 +30918,7 @@
         <v>46265</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -30990,7 +30991,7 @@
         <v>46265</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31063,7 +31064,7 @@
         <v>46265</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31136,7 +31137,7 @@
         <v>46268</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31209,7 +31210,7 @@
         <v>46268</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31282,7 +31283,7 @@
         <v>45977</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31355,7 +31356,7 @@
         <v>46272</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31428,7 +31429,7 @@
         <v>46278</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31501,7 +31502,7 @@
         <v>46280</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31574,7 +31575,7 @@
         <v>46286</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31647,7 +31648,7 @@
         <v>46246</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31720,7 +31721,7 @@
         <v>45982</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31793,7 +31794,7 @@
         <v>46084</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31866,7 +31867,7 @@
         <v>46293</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31939,7 +31940,7 @@
         <v>46255</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32012,7 +32013,7 @@
         <v>46255</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32085,7 +32086,7 @@
         <v>46300</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32158,7 +32159,7 @@
         <v>46253</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32231,7 +32232,7 @@
         <v>46113</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32304,7 +32305,7 @@
         <v>46302</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32377,7 +32378,7 @@
         <v>46260</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32450,7 +32451,7 @@
         <v>46304</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32523,7 +32524,7 @@
         <v>44658</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32596,7 +32597,7 @@
         <v>45235</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32669,7 +32670,7 @@
         <v>45316</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32742,7 +32743,7 @@
         <v>45527</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32815,7 +32816,7 @@
         <v>45440</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32888,7 +32889,7 @@
         <v>45471</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -32961,7 +32962,7 @@
         <v>45440</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33034,7 +33035,7 @@
         <v>45440</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33107,7 +33108,7 @@
         <v>45558</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33180,7 +33181,7 @@
         <v>45373</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33253,7 +33254,7 @@
         <v>45330</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33326,7 +33327,7 @@
         <v>45373</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33399,7 +33400,7 @@
         <v>45387</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33472,7 +33473,7 @@
         <v>45373</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33545,7 +33546,7 @@
         <v>45440</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33618,7 +33619,7 @@
         <v>45687</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33691,7 +33692,7 @@
         <v>45440</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33764,7 +33765,7 @@
         <v>44928</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33837,7 +33838,7 @@
         <v>44971</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33910,7 +33911,7 @@
         <v>45440</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -33983,7 +33984,7 @@
         <v>45791</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34056,7 +34057,7 @@
         <v>45791</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34129,7 +34130,7 @@
         <v>45791</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45798</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45426</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45820</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>44722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>44977</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>44725</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45330</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>44988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45350</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>46308</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>46308</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>46265</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45471</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>46065</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44657</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44580</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44804</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>45019</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45079</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44984</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45917</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>46056</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>46084</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45672</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44596</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44942</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>46289</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45223</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>46293</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45573</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>46265</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>45860</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45440</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45687</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44971</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>46084</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44840</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>44592</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>44883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44489</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44564</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44514</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44532</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44536</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44837</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44879</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44711</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44652</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44795</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44489</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44489</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44636</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44811</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44811</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44516</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44580</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44748</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44658</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>44812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44853</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45288</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44849</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45426</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45362</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44988</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45001</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44861</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44949</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45159</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45770</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44958</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>44613</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>44890</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44792</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45098</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>44910</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45350</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44879</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45240</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45001</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44683</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44683</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45155</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45327</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45075</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45309</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44987</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>44998</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45051</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>44593</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45567</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45219</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45198</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45163</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45624</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45050</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45208</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45195</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45407</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45330</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45695</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45532</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44861</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44516</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45063</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45251</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>44949</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44827</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>44980</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45250</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45000</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44741</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44536</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45271</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44944</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45225</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45583</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45838</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>46092</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44739</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44965</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44942</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>46092</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>45222</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44914</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>45895</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45330</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45075</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>44795</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45271</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44795</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>46066</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44902</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45826</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45250</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44671</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45798</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45145</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45260</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45916</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45917</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45917</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45917</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>46146</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45736</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45924</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45925</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45925</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45335</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45196</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45224</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45016</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45252</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45908</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45947</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45946</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44490</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45951</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45408</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45330</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45447</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44600</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45672</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44613</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44706</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>44942</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44998</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45966</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45222</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45132</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45329</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45139</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45369</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45001</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45624</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46111</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45054</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44841</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46111</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45988</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45194</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45798</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44495</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45716</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45208</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45208</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45040</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46001</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46001</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45288</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45288</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45182</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44984</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45720</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>46174</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45404</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45988</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45790</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45222</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44694</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45308</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45145</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>46174</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>46174</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44988</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44827</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45250</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45250</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45196</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>46035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44883</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>46167</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44949</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>44992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45155</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45201</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46059</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45440</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>46167</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44958</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>46084</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46083</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>46084</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44893</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>44826</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>44725</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44600</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>46090</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45029</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46092</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45096</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46119</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44529</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45194</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45113</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45546</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46106</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45093</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45093</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46106</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44881</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45328</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45610</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45001</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45113</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>46203</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>44958</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45250</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45250</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45425</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45243</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>44739</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45113</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44722</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44977</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44790</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45614</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44985</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45093</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>45093</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44949</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45552</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>44950</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46217</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46218</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>46218</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45518</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45008</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45178</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>44637</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>44900</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45695</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45977</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44851</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44519</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46272</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44511</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45601</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45082</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45426</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45012</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45583</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>46278</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45716</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45219</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>46280</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45225</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45223</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45280</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45513</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45513</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45243</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45370</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45636</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45734</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45210</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45182</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>46286</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45324</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45474</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44657</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45194</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45362</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>46246</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45645</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44502</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>45027</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45982</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45323</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>46293</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>45093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>46084</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45352</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>45198</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45167</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45167</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>46255</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>46255</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>46253</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>46113</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>44986</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45713</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45299</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>45474</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45694</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45665</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45785</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>46300</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45645</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45012</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45330</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>45474</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44679</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45527</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45665</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>46302</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>46260</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>46304</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45798</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45551</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45488</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>46265</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45618</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>46265</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>46309</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46309</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>46265</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46268</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>46268</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45820</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45827</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>45839</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45860</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45869</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45869</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45869</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45880</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45713</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45880</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45235</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45527</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45440</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44658</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45471</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45440</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45440</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45558</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45373</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45330</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45373</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45373</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45687</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45440</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>44928</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>44971</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45440</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45791</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45791</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45791</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45798</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45426</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45820</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>44722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45350</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>44977</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>44725</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45330</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44939</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>44988</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45350</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>46308</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>46308</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>46265</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45471</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>46065</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44657</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44580</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44804</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>45019</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45079</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44984</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45917</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>46056</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>46084</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>46112</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45672</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>44596</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>44942</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>46289</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>45223</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>46293</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45573</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>46265</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>45860</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45440</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45687</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44971</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>46084</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44840</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>44592</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44530</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44839</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>44883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44489</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44517</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44564</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44514</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44532</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44536</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44837</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44879</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44711</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44652</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44795</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44489</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44489</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44636</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>44811</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44811</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44516</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44580</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44748</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44658</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>44812</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44853</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>45288</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44849</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>45426</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>45362</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44988</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45001</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>44861</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44949</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>44763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45159</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>45036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45770</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44958</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>44613</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>44890</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44792</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45098</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>44910</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45350</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44879</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45240</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45001</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45001</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44683</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44683</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45155</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45327</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>45075</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45309</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>44987</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>44998</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45051</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>44593</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45567</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45219</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45198</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45163</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45624</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45050</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45208</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45195</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45407</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45330</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45695</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45532</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44861</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44516</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45063</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45251</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>44949</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44827</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44889</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>44980</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45250</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45000</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44741</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44536</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45271</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>44944</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45225</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45583</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>45838</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>46092</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>44739</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44965</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>44942</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>46092</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>45222</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>44914</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>45895</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45330</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45075</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>44795</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45271</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>44795</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>46066</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44902</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45826</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45250</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44671</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45798</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45145</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45260</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45916</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45917</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45917</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45917</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>46146</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>45736</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45924</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45925</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45925</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45335</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45196</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45224</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45016</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45252</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45908</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45947</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45946</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44490</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45951</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45408</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45330</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45447</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44600</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45672</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>44613</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44706</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>44942</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>44998</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45966</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45222</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>44965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45132</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45329</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45139</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45369</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45001</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>45624</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46111</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45054</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44841</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46111</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45988</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45194</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45798</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>44495</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45716</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45208</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45208</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45040</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46001</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>46001</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45288</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45288</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45182</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>44984</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45720</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>46174</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45058</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>45404</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45988</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45790</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45222</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>44694</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>45308</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45145</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>46174</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>46174</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>44988</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>44827</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45250</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>45250</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46035</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45196</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>46035</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>44943</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>44883</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>46167</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>44949</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>44992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>45155</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>45201</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46059</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45440</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>46167</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>44958</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>46084</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>46083</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>46084</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>44893</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>44826</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>44725</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>44600</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>46090</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45029</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>46092</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45096</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>46119</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44529</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45194</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45113</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45546</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46106</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45093</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45093</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>46106</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44881</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45328</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45610</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45001</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44938</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45084</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45113</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>46203</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>44958</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45250</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45250</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45425</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45243</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>44739</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45113</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44722</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>45253</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44977</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44790</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45614</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>44985</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45093</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>45093</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44949</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45552</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>44950</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25723,7 +25723,7 @@
         <v>46217</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46218</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>46218</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45518</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45008</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45178</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>44637</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>44900</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45695</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45977</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44851</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44519</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46272</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44511</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45601</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45082</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45426</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45012</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45583</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>46278</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45716</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45219</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>46280</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45225</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45223</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45280</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45513</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>45513</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45243</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45370</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45636</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45734</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>45210</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45182</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>46286</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45324</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>45252</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45474</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>44657</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45194</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45182</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>45362</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>46246</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28867,7 +28867,7 @@
         <v>45645</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44502</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>45027</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45982</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45323</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>46293</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>45093</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>46084</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45352</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>45198</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45167</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45167</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>46255</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>46255</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29889,7 +29889,7 @@
         <v>46253</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>46113</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         <v>44986</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>45713</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>45299</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30254,7 +30254,7 @@
         <v>45474</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30327,7 +30327,7 @@
         <v>45694</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30400,7 +30400,7 @@
         <v>45665</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45785</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30546,7 +30546,7 @@
         <v>46300</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45645</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45012</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45330</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>45474</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>44679</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30984,7 +30984,7 @@
         <v>45527</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45665</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>46302</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31203,7 +31203,7 @@
         <v>46260</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>46304</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31349,7 +31349,7 @@
         <v>45798</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31422,7 +31422,7 @@
         <v>45551</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45488</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>46265</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31641,7 +31641,7 @@
         <v>45618</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>46265</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>46309</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>46309</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>46265</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>46268</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>46268</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45820</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45827</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>45839</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>45860</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>45869</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45869</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45869</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>45880</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45713</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45880</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45235</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45316</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45527</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45440</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>44658</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45471</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45440</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45440</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45558</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45373</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45330</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45373</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45387</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45373</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>45440</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45687</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45440</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>44928</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>44971</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45440</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45791</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34415,7 +34415,7 @@
         <v>45791</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45791</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45798</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45426</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45820</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>44722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45350</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>44977</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>44725</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45330</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46308</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>46308</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>44939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>46265</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45350</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45471</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>46065</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44657</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45079</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44942</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>45223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46056</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>46289</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46293</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46084</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45860</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>46112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>46265</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>45672</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44580</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>45019</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44984</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44596</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>44804</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45440</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45687</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44971</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>46084</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44840</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>44592</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44839</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>44883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44564</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44514</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44532</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44536</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44837</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44879</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44711</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44652</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44599</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44636</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44811</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44516</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45075</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44977</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44580</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44748</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44658</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45335</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45222</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44739</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44795</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44657</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45895</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45251</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45323</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45532</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44725</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45610</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44792</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45222</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44958</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45916</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>46111</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45040</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45210</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45917</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>46111</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45798</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45426</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44593</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45924</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44958</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45925</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44519</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45001</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45001</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45925</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45222</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45369</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45330</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45288</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45370</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45988</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45224</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44949</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>46174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45624</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>46174</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>46174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45093</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45139</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45327</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45250</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45250</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45946</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>46167</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45058</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45309</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45951</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44883</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45716</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45695</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45182</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>46167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45966</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45223</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44826</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45328</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45308</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>46119</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45182</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45250</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44671</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>45036</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>45012</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44949</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45447</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45518</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45222</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45407</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44889</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45208</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45243</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45001</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>45001</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45253</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45988</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44942</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45096</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45054</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45770</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>46217</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45404</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45408</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>46218</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>46218</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45583</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45694</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45474</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45713</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45299</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>46001</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44853</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>46001</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45977</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45665</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45474</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45012</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>46278</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44849</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>46280</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45785</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45645</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44679</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45330</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45790</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45527</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45665</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46286</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46035</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45798</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45618</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45551</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45488</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46246</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45982</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46084</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>46059</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46293</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44942</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>44949</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45820</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45827</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>46083</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46084</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>46084</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46255</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>46255</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46300</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>46090</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>46253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>46092</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>46092</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45839</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44516</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>44943</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>44529</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>46113</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>46106</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>46106</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>46302</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45860</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>46260</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45869</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45869</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45869</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>46304</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44511</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45880</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45880</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>46265</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>46265</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45713</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45352</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>46265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>46092</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>46092</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44881</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>44600</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45838</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45425</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>46309</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>46309</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45098</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45001</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45001</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>46268</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45546</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45008</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45636</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45113</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>46268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45826</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>46066</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45930</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>46272</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>46293</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45155</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45583</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>45720</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>46146</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44613</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45426</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>45082</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45075</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45271</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45271</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45908</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>44998</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45113</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>45113</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45614</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44958</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44495</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45324</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45000</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45672</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45145</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45093</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45178</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>44739</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44776</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44985</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44694</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>44683</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>44683</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45243</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>44988</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44841</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45155</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44827</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45113</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45474</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>44763</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44914</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44890</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44893</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45222</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44827</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>44950</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45350</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44949</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45329</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44965</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45250</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45145</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44790</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45051</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45567</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>44910</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>44938</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44987</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44502</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45288</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45016</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45513</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45513</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45440</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45734</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45084</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44967</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45330</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45167</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45167</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44536</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45601</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45201</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45063</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45624</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45027</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44795</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44998</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45194</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45050</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45225</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45196</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>44879</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45208</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44861</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>44861</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45196</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44722</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45195</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45252</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45250</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45161</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45159</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45182</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45240</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45194</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45695</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45208</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45716</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45252</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45260</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>44741</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45225</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45219</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45219</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45219</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>44706</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45330</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45552</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45198</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45280</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>44851</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45194</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>44900</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45145</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44965</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45132</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45362</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45362</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44879</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44613</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44600</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45093</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45093</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>44658</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45235</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45316</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45527</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45440</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45471</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45440</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45440</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45558</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45373</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45330</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45373</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45387</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45373</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45440</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45687</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45440</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>44928</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44971</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45440</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45791</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45791</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45791</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>

--- a/Översikt TORSÅS.xlsx
+++ b/Översikt TORSÅS.xlsx
@@ -601,7 +601,7 @@
         <v>44971</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>45977</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45373</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>45798</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>45426</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45820</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>44722</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>45202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45350</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>44977</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>44725</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45330</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>46084</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>46308</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>46308</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>44939</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>46265</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45350</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>44988</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45471</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>44928</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44928</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>46065</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44657</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>44571</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45079</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>44942</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>45223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46056</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>46289</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46293</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>46084</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45860</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>46112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>46265</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>45672</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44580</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>45019</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44984</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44596</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>44804</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>45253</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45387</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>45440</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45687</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44971</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>46084</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44840</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44763</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44846</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>44592</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44839</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44586</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44862</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>44883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>44595</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44517</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44564</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44514</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>44532</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>44536</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44837</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44879</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>44711</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44652</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44599</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44636</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>44811</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>44811</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>44516</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>45075</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44977</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44580</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>44748</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>44658</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
         <v>44812</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>45335</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>45222</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44739</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44795</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         <v>44637</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>45196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44657</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45895</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45251</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45323</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45532</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44725</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45610</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>44792</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45222</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44958</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>45916</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>46111</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>45040</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45210</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>45917</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>45917</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>46111</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>45798</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>45426</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44593</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45924</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44958</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>45925</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44519</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45001</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45001</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45925</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45222</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45369</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>45330</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45288</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45370</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45988</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45224</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44949</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>46174</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45624</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>46174</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>46174</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45093</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45139</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45327</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45250</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>45250</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45946</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>46167</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45058</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>45309</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45951</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44883</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>45716</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>45695</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>45182</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>46167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45966</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45223</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44826</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>45328</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>45308</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>46119</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45182</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
         <v>45250</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44671</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>45036</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14471,7 +14471,7 @@
         <v>45012</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14544,7 +14544,7 @@
         <v>44949</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45447</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14690,7 +14690,7 @@
         <v>45518</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>46203</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45222</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45407</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44889</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45208</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45243</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45001</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>45001</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45253</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45988</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44942</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45096</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45054</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45770</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>46217</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45404</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45408</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>46218</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>46218</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45583</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45694</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45474</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45713</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45299</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>46001</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44853</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>46001</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45977</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45665</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45474</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45012</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>46278</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44849</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>46280</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45785</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45645</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44679</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45330</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45790</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45527</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>45665</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>46286</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46035</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45798</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45618</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45551</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45488</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46246</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>45982</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46084</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>46059</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46293</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44942</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>44949</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45820</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>45827</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>46083</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46084</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>46084</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46255</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>46255</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46300</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>46090</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>46253</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>46092</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>46092</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>45839</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>44516</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>44943</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>44902</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>44529</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>46113</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>46106</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>46106</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>46302</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45860</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>46260</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45869</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20749,7 +20749,7 @@
         <v>45869</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20822,7 +20822,7 @@
         <v>45869</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20895,7 +20895,7 @@
         <v>46304</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>44511</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>44988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>45880</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         <v>45880</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21260,7 +21260,7 @@
         <v>46265</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>46265</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>45713</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45352</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>46265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>46092</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>46092</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44881</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>44600</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45838</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>45425</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>46309</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>46309</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45098</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45001</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45001</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>46268</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45546</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45008</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45636</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45113</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>46268</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45826</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>46066</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>45930</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23085,7 +23085,7 @@
         <v>46272</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23158,7 +23158,7 @@
         <v>46293</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45155</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45583</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>45720</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>46146</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44613</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45426</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>45082</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45075</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45271</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45271</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>45908</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>44998</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45113</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>45113</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45614</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>44958</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>44495</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45324</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45000</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>45672</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45145</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>44992</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45093</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>45178</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>44739</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>44776</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>44985</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25207,7 +25207,7 @@
         <v>44694</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>44683</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>44683</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>45243</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>44988</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45029</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44841</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45155</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44827</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45113</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45113</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45474</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>44763</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26229,7 +26229,7 @@
         <v>44914</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44890</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44893</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>45222</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26521,7 +26521,7 @@
         <v>44827</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26594,7 +26594,7 @@
         <v>44944</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26667,7 +26667,7 @@
         <v>44950</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45350</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44949</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45329</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>44965</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45250</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>44980</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45145</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44790</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45051</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45567</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>44910</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>44938</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>44987</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>44502</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45288</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>45016</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45513</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45513</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45440</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45734</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45084</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44967</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45330</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45167</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45167</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44536</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45601</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45201</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45063</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45624</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45027</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44795</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>44998</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45194</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45050</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45225</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>45196</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>44879</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45208</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>44861</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>44861</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>45196</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>44722</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>45195</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45252</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45250</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>45161</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45159</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45182</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45240</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45194</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>45695</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30614,7 +30614,7 @@
         <v>45208</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45716</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45252</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45260</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>44741</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45225</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45219</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>45219</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45219</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>44706</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45330</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45552</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45198</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45280</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>44851</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45194</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>44900</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45145</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>44965</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45132</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>45362</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45362</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32298,7 +32298,7 @@
         <v>44879</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>44613</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32444,7 +32444,7 @@
         <v>44600</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>45093</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>45093</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>44658</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45235</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45316</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45527</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45440</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45471</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45440</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45440</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45558</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45373</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45330</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45373</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>45387</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45373</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>45440</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45687</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45440</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33904,7 +33904,7 @@
         <v>44928</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44971</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45440</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45791</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45791</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
         <v>45791</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
